--- a/outputs/ranker/baseline/ranker_feature_importance.xlsx
+++ b/outputs/ranker/baseline/ranker_feature_importance.xlsx
@@ -441,7 +441,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.5242899508664018</v>
+        <v>0.5295280981156625</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -449,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.4636877694261007</v>
+        <v>0.4684261329512984</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.008807235762819519</v>
+        <v>0.001717338277104945</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -465,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.003215043944677783</v>
+        <v>0.0003284306559341352</v>
       </c>
     </row>
     <row r="6" spans="1:2">
